--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-03-2026.xlsx
@@ -588,12 +588,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£23.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£10.25</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£12.07</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£15.24</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£15.84</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.67</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£23.15</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£46.64</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.05</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£22.09</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£25.07</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£57.31</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£27.59</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£27.15</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£32.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£33.38</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£39.79</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£47.29</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£41.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£89.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£779.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£1019.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£51.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£28.12</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£34.75</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£79.58</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£36.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£42.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£45.74</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£43.75</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£924.00</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£43.69</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1199.84</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1336.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1359.84</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
